--- a/docs/제품 TEST 관리.xlsx
+++ b/docs/제품 TEST 관리.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\product_test_tracing_system\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A32857-1E6F-46F8-B8E3-EBD149EB530B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D25D89-2F6F-498E-A21D-AB83F2DECA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{421B0B10-1399-475F-B14E-2C2D39CF6739}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{421B0B10-1399-475F-B14E-2C2D39CF6739}"/>
   </bookViews>
   <sheets>
-    <sheet name="Config ID Map" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Config ID 관리" sheetId="1" r:id="rId1"/>
     <sheet name="테스트 환경" sheetId="9" state="hidden" r:id="rId2"/>
     <sheet name="TRACE ID" sheetId="10" r:id="rId3"/>
     <sheet name="HRK" sheetId="3" r:id="rId4"/>
@@ -21,7 +21,7 @@
     <sheet name="HTR" sheetId="5" r:id="rId6"/>
     <sheet name="HDR" sheetId="6" r:id="rId7"/>
     <sheet name="HDC" sheetId="7" r:id="rId8"/>
-    <sheet name="WIFI 통신 테스트 문제점 관리" sheetId="8" r:id="rId9"/>
+    <sheet name="문제점 관리" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="446">
   <si>
     <t>HRK-9000A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1651,10 +1651,6 @@
     <t>DR Connect OFF 확인</t>
   </si>
   <si>
-    <t>1. AP 연결 후 (HDC-001), Web service 탭에서 DR connect OFF 클릭
-2. HDR과 Wi-Fi 연결 후 HDR에서 차트 동작을 진행해본다.</t>
-  </si>
-  <si>
     <t>HDR에서 연결이 되지 않으며 차트 변경이 되지 않음.</t>
   </si>
   <si>
@@ -2039,9 +2035,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>STR(Step to Reproducing)</t>
-  </si>
-  <si>
     <t>Actual Result</t>
   </si>
   <si>
@@ -2054,10 +2047,6 @@
   </si>
   <si>
     <t>Test Config 재현성 데이터</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Test STR(Step to Reproducing)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2120,6 +2109,48 @@
 or
 Band Steering: Off
 SSID 분리표기확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test Procedure</t>
+  </si>
+  <si>
+    <t>Test Senario ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"REF/KER 측정 MODE 화면" 좌측상단 차트번호와 OP Basic Operation 화면 좌측상단 LOAD DATA의 차트번호 비교결과, 측정화면 차트번호가 1이 더 큰지 확인
+TBD
+- HDR( Server )에서 데이터를 수신 확인한다. 
+(OP 어디에서 수신이미지 확인하기 위한 위치 공유요청)
+TBD
+- Patient ID가 동일한 마이봄샘 이미지가 저장되어 있었다면, 덮어씀
+(덮어쓰는 이미지 전 후 비교방법 공유요청) 
+TBD
+- 같은 환자번호에서, 여러 번 보냈을때 이미지가 덮어쓰여지는지 확인 필요.
+(같은 환자번호에서, 여러 번 보내는 방법 공유요청)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"REF/KER 측정 MODE 화면" 좌측상단 차트번호와 OP Basic Operation 화면 좌측상단 LOAD DATA의 차트번호 비교결과, 측정화면 차트번호가 1이 더 큰지 확인
+TBD
+- HDR( Server )에서 데이터를 수신 확인한다. 
+(OP 어디에서 수신이미지 확인하기 위한 위치 공유요청)
+TBD
+- Patient ID가 동일한 마이봄샘 이미지가 저장되어 있었다면, 덮어씀
+(덮어쓰는 이미지 전 후 비교방법 공유요청) 
+TBD
+- 같은 환자번호에서, 여러 번 보냈을때 이미지가 덮어쓰여지는지 확인 필요.
+(같은 환자번호에서, 여러 번 보내는 방법 공유요청)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. AP 연결 후 (HDC-001), Web service 탭에서 DR connect OFF 클릭
+2. HDR과 Wi-Fi 연결 후 HDR에서 차트 동작을 진행해본다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test Case ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2130,7 +2161,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2214,6 +2245,14 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2396,12 +2435,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2454,6 +2490,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2487,60 +2571,162 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="강조색1" xfId="1" builtinId="29"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2869,588 +3055,588 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="43" t="s">
-        <v>425</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43" t="s">
+      <c r="A1" s="32" t="s">
+        <v>423</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="27" t="s">
         <v>426</v>
       </c>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="40" t="s">
+      <c r="B2" s="27" t="s">
+        <v>411</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>419</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>409</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>412</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>369</v>
+      </c>
+      <c r="L2" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>406</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+    </row>
+    <row r="11" spans="1:13" ht="85">
+      <c r="A11" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="F11" s="18"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="102" customHeight="1">
+      <c r="A12" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="F12" s="18"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="M12" s="18" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="119">
+      <c r="A13" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="M13" s="18" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="170">
+      <c r="A14" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="F14" s="18"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="M14" s="18" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="85">
+      <c r="A15" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="I15" s="25"/>
+      <c r="J15" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="M15" s="18" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="16"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="17" t="s">
         <v>429</v>
       </c>
-      <c r="B2" s="40" t="s">
-        <v>412</v>
-      </c>
-      <c r="C2" s="40" t="s">
-        <v>416</v>
-      </c>
-      <c r="D2" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="E2" s="40" t="s">
-        <v>420</v>
-      </c>
-      <c r="F2" s="40" t="s">
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="16"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="30" t="s">
         <v>410</v>
       </c>
-      <c r="G2" s="40" t="s">
-        <v>415</v>
-      </c>
-      <c r="H2" s="40" t="s">
-        <v>413</v>
-      </c>
-      <c r="I2" s="40" t="s">
-        <v>414</v>
-      </c>
-      <c r="J2" s="41" t="s">
-        <v>440</v>
-      </c>
-      <c r="K2" s="41" t="s">
-        <v>370</v>
-      </c>
-      <c r="L2" s="41" t="s">
+      <c r="B19" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="45" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="D19" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="16"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="17" t="s">
+      <c r="C20" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B4" s="17" t="s">
+      <c r="D20" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="17" t="s">
+      <c r="C21" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="D21" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="C22" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>363</v>
-      </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>407</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-    </row>
-    <row r="11" spans="1:13" ht="85">
-      <c r="A11" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>366</v>
-      </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="31" t="s">
-        <v>371</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>442</v>
-      </c>
-      <c r="J11" s="35" t="s">
-        <v>441</v>
-      </c>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30" t="s">
-        <v>439</v>
-      </c>
-      <c r="M11" s="30" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="102" customHeight="1">
-      <c r="A12" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>404</v>
-      </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="I12" s="32" t="s">
-        <v>381</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>389</v>
-      </c>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="M12" s="30" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="187">
-      <c r="A13" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="31" t="s">
-        <v>382</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>390</v>
-      </c>
-      <c r="K13" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="L13" s="30" t="s">
-        <v>376</v>
-      </c>
-      <c r="M13" s="30" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="289">
-      <c r="A14" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>368</v>
-      </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="I14" s="32" t="s">
-        <v>383</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>401</v>
-      </c>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30" t="s">
-        <v>400</v>
-      </c>
-      <c r="M14" s="30" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="85">
-      <c r="A15" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="32" t="s">
-        <v>377</v>
-      </c>
-      <c r="I15" s="37"/>
-      <c r="J15" s="30" t="s">
-        <v>403</v>
-      </c>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30" t="s">
-        <v>402</v>
-      </c>
-      <c r="M15" s="30" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>430</v>
-      </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="17"/>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>431</v>
-      </c>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="17"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="17"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="17" t="s">
+      <c r="D22" s="16" t="s">
         <v>433</v>
       </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="17"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>434</v>
-      </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>435</v>
-      </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>436</v>
-      </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3458,6 +3644,11 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:M22">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3478,156 +3669,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
-      <c r="A1" s="38" t="s">
-        <v>393</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="A1" s="33" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="21.5" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="28" t="s">
+        <v>372</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>387</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>386</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="119">
+      <c r="A3" s="24">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="51">
+      <c r="A4" s="24">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="E2" s="41" t="s">
-        <v>387</v>
-      </c>
-      <c r="F2" s="41" t="s">
+      <c r="E4" s="19" t="s">
         <v>379</v>
       </c>
-      <c r="G2" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="119">
-      <c r="A3" s="36">
-        <v>1</v>
-      </c>
-      <c r="B3" s="30" t="s">
+      <c r="F4" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:7" ht="85">
+      <c r="A5" s="24">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="170">
+      <c r="A6" s="24">
+        <v>4</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7" spans="1:7" ht="85">
+      <c r="A7" s="24">
+        <v>5</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="C3" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31" t="s">
-        <v>378</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="G3" s="30"/>
-    </row>
-    <row r="4" spans="1:7" ht="51">
-      <c r="A4" s="36">
-        <v>2</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>404</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>389</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>381</v>
-      </c>
-      <c r="G4" s="30"/>
-    </row>
-    <row r="5" spans="1:7" ht="85">
-      <c r="A5" s="36">
-        <v>3</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="C5" s="30" t="s">
+      <c r="C7" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E7" s="20" t="s">
         <v>376</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="F7" s="25"/>
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:7" ht="34">
+      <c r="A8" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23" t="s">
         <v>390</v>
       </c>
-      <c r="E5" s="31" t="s">
-        <v>382</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="170">
-      <c r="A6" s="36">
-        <v>4</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>368</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>400</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>401</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>383</v>
-      </c>
-      <c r="G6" s="30"/>
-    </row>
-    <row r="7" spans="1:7" ht="85">
-      <c r="A7" s="36">
-        <v>5</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>402</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>403</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>377</v>
-      </c>
-      <c r="F7" s="37"/>
-      <c r="G7" s="30"/>
-    </row>
-    <row r="8" spans="1:7" ht="34">
-      <c r="A8" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>392</v>
-      </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35" t="s">
-        <v>391</v>
-      </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3656,100 +3847,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="42" t="s">
-        <v>424</v>
-      </c>
-      <c r="F1" s="42" t="s">
+      <c r="E1" s="29" t="s">
         <v>422</v>
       </c>
-      <c r="G1" s="42" t="s">
-        <v>423</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="F1" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>421</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="34" t="s">
+        <v>358</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>404</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="34.5" thickBot="1">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>405</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="34.5" thickBot="1">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="8"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" ht="136.5" thickBot="1">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="4" t="s">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="8"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3769,3315 +3960,3787 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B22A724-A177-408E-A72A-AA4756D6BFC4}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultColWidth="52.9140625" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="8.4140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.9140625" customWidth="1"/>
     <col min="2" max="2" width="27.58203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="52.58203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="77.9140625" customWidth="1"/>
     <col min="5" max="5" width="50.33203125" customWidth="1"/>
-    <col min="6" max="6" width="52.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="52.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="52.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.9140625" customWidth="1"/>
+    <col min="7" max="7" width="110.25" customWidth="1"/>
+    <col min="8" max="8" width="133.25" customWidth="1"/>
+    <col min="9" max="9" width="52.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.6640625" customWidth="1"/>
+    <col min="11" max="11" width="75.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A1" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="42" t="s">
-        <v>429</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>427</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>428</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="E1" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>425</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A2" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="34" t="s">
+        <v>358</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>397</v>
+      </c>
+      <c r="F2" s="37" t="str">
+        <f>_xlfn.CONCAT("TC-", A2)</f>
+        <v>TC-HRK-001</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="19" t="s">
+      <c r="H3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" ht="85.5" thickBot="1">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="7"/>
+    </row>
+    <row r="5" spans="1:11" ht="136.5" thickBot="1">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="19" t="s">
+      <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" spans="1:11" ht="153.5" thickBot="1">
+      <c r="A6" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A7" s="38"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A9" s="38"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A10" s="39"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:11" ht="153.5" thickBot="1">
+      <c r="A11" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" ht="136.5" thickBot="1">
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A14" s="39"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A15" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" ht="272.5" thickBot="1">
+      <c r="A16" s="39"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A17" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" ht="238.5" thickBot="1">
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A19" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="J19" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" ht="238.5" thickBot="1">
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A21" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="J21" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K21" s="7"/>
+    </row>
+    <row r="22" spans="1:11" ht="238.5" thickBot="1">
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="7"/>
+    </row>
+    <row r="23" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A23" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="J23" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="7"/>
+    </row>
+    <row r="24" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="7"/>
+    </row>
+    <row r="25" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A25" s="38"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="7"/>
+    </row>
+    <row r="26" spans="1:11" ht="170.5" thickBot="1">
+      <c r="A26" s="39"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I26" s="36"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="7"/>
+    </row>
+    <row r="27" spans="1:11" ht="136.5" customHeight="1" thickBot="1">
+      <c r="A27" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="F27" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="J27" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="170.5" customHeight="1" thickBot="1">
+      <c r="A28" s="38"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="7"/>
+    </row>
+    <row r="29" spans="1:11" ht="85.5" customHeight="1" thickBot="1">
+      <c r="A29" s="38"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="7"/>
+    </row>
+    <row r="30" spans="1:11" ht="68.5" customHeight="1" thickBot="1">
+      <c r="A30" s="38"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="7"/>
+    </row>
+    <row r="31" spans="1:11" ht="51.5" customHeight="1" thickBot="1">
+      <c r="A31" s="38"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32" spans="1:11" ht="119.5" customHeight="1" thickBot="1">
+      <c r="A32" s="38"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="7"/>
+    </row>
+    <row r="33" spans="1:11" ht="153.5" customHeight="1" thickBot="1">
+      <c r="A33" s="38"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="7"/>
+    </row>
+    <row r="34" spans="1:11" ht="68.5" customHeight="1" thickBot="1">
+      <c r="A34" s="38"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="7"/>
+    </row>
+    <row r="35" spans="1:11" ht="136.5" customHeight="1" thickBot="1">
+      <c r="A35" s="38"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="F35" s="38"/>
+      <c r="G35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I35" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="J35" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="170.5" customHeight="1" thickBot="1">
+      <c r="A36" s="38"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="7"/>
+    </row>
+    <row r="37" spans="1:11" ht="85.5" customHeight="1" thickBot="1">
+      <c r="A37" s="38"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="7"/>
+    </row>
+    <row r="38" spans="1:11" ht="68.5" customHeight="1" thickBot="1">
+      <c r="A38" s="38"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="7"/>
+    </row>
+    <row r="39" spans="1:11" ht="51.5" customHeight="1" thickBot="1">
+      <c r="A39" s="38"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="7"/>
+    </row>
+    <row r="40" spans="1:11" ht="119.5" customHeight="1" thickBot="1">
+      <c r="A40" s="38"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="49"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="7"/>
+    </row>
+    <row r="41" spans="1:11" ht="153.5" customHeight="1" thickBot="1">
+      <c r="A41" s="38"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="7"/>
+    </row>
+    <row r="42" spans="1:11" ht="68.5" customHeight="1" thickBot="1">
+      <c r="A42" s="39"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="7"/>
+    </row>
+    <row r="43" spans="1:11" ht="136.5" thickBot="1">
+      <c r="A43" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="F43" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I43" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="J43" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="34.5" thickBot="1">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:10" ht="136.5" thickBot="1">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" ht="153.5" thickBot="1">
-      <c r="A5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10" ht="221.5" thickBot="1">
-      <c r="A6" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="34.5" thickBot="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="4" t="s">
+      <c r="K43" s="7"/>
+    </row>
+    <row r="44" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A44" s="38"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="10"/>
+    </row>
+    <row r="45" spans="1:11" ht="85.5" thickBot="1">
+      <c r="A45" s="38"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I45" s="35"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="10"/>
+    </row>
+    <row r="46" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A46" s="38"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H46" s="10"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="10"/>
+    </row>
+    <row r="47" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A47" s="38"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I47" s="35"/>
+      <c r="J47" s="35"/>
+      <c r="K47" s="10"/>
+    </row>
+    <row r="48" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A48" s="38"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="38"/>
+      <c r="G48" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I48" s="35"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="10"/>
+    </row>
+    <row r="49" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A49" s="38"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="35"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I49" s="35"/>
+      <c r="J49" s="35"/>
+      <c r="K49" s="10"/>
+    </row>
+    <row r="50" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A50" s="39"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" ht="221.5" thickBot="1">
-      <c r="A11" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="170.5" thickBot="1">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A15" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" ht="221.5" thickBot="1">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A17" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" ht="221.5" thickBot="1">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A19" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" ht="221.5" thickBot="1">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A21" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" ht="221.5" thickBot="1">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A23" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10" ht="34.5" thickBot="1">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="8"/>
-    </row>
-    <row r="26" spans="1:10" ht="221.5" thickBot="1">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="8"/>
-    </row>
-    <row r="27" spans="1:10" ht="136.5" thickBot="1">
-      <c r="A27" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="170.5" thickBot="1">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="8"/>
-    </row>
-    <row r="29" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A29" s="23"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="8"/>
-    </row>
-    <row r="30" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A30" s="23"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="8"/>
-    </row>
-    <row r="31" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="8"/>
-    </row>
-    <row r="32" spans="1:10" ht="119.5" thickBot="1">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="8"/>
-    </row>
-    <row r="33" spans="1:10" ht="153.5" thickBot="1">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="8"/>
-    </row>
-    <row r="34" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A34" s="24"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="H50" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="8"/>
-    </row>
-    <row r="35" spans="1:10" ht="187.5" thickBot="1">
-      <c r="A35" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D35" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H35" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="I35" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J35" s="8"/>
-    </row>
-    <row r="36" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="11"/>
-    </row>
-    <row r="37" spans="1:10" ht="119.5" thickBot="1">
-      <c r="A37" s="23"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="11"/>
-    </row>
-    <row r="38" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="G38" s="11"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="11"/>
-    </row>
-    <row r="39" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="11"/>
-    </row>
-    <row r="40" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="11"/>
-    </row>
-    <row r="41" spans="1:10" ht="119.5" thickBot="1">
-      <c r="A41" s="23"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="11"/>
-    </row>
-    <row r="42" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A42" s="24"/>
-      <c r="B42" s="24"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="11"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="I2:I4"/>
+  <mergeCells count="83">
+    <mergeCell ref="I27:I34"/>
+    <mergeCell ref="J27:J34"/>
+    <mergeCell ref="A27:A42"/>
+    <mergeCell ref="B27:B42"/>
+    <mergeCell ref="C27:C42"/>
+    <mergeCell ref="D27:D42"/>
+    <mergeCell ref="F27:F42"/>
+    <mergeCell ref="E27:E34"/>
+    <mergeCell ref="J35:J42"/>
+    <mergeCell ref="A43:A50"/>
+    <mergeCell ref="B43:B50"/>
+    <mergeCell ref="C43:C50"/>
+    <mergeCell ref="D43:D50"/>
+    <mergeCell ref="E43:E50"/>
+    <mergeCell ref="I43:I50"/>
+    <mergeCell ref="J43:J50"/>
+    <mergeCell ref="E35:E42"/>
+    <mergeCell ref="I35:I42"/>
+    <mergeCell ref="F43:F50"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="I23:I26"/>
+    <mergeCell ref="J23:J26"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="E11:E14"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="J2:J4"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="C6:C10"/>
     <mergeCell ref="D6:D10"/>
     <mergeCell ref="E6:E10"/>
-    <mergeCell ref="H6:H10"/>
     <mergeCell ref="I6:I10"/>
+    <mergeCell ref="J6:J10"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="E2:E4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="E11:E14"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="H23:H26"/>
-    <mergeCell ref="I23:I26"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="I27:I34"/>
-    <mergeCell ref="A35:A42"/>
-    <mergeCell ref="B35:B42"/>
-    <mergeCell ref="C35:C42"/>
-    <mergeCell ref="D35:D42"/>
-    <mergeCell ref="E35:E42"/>
-    <mergeCell ref="H35:H42"/>
-    <mergeCell ref="I35:I42"/>
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="B27:B34"/>
-    <mergeCell ref="C27:C34"/>
-    <mergeCell ref="D27:D34"/>
-    <mergeCell ref="E27:E34"/>
-    <mergeCell ref="H27:H34"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="F6:F10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:E26 A43:E50 E35:E42 G35:K50 G1:K26">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:E27 B28:E34 G27:K34">
+    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",A27)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F26 F43:F50">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F27)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E004DF70-132F-4F82-9E1F-34735E113B71}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="52.9140625" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.9140625" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="52.58203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="52.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="48.58203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.9140625" customWidth="1"/>
+    <col min="8" max="8" width="52.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="48.58203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A1" s="45" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="42" t="s">
-        <v>429</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>427</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>428</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>425</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A2" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="34" t="s">
+        <v>395</v>
+      </c>
+      <c r="F2" s="37" t="str">
+        <f>_xlfn.CONCAT("TC-", A2)</f>
+        <v>TC-HLM-001</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K2" s="10"/>
+    </row>
+    <row r="3" spans="1:11" ht="136.5" thickBot="1">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="36"/>
+      <c r="J3" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:11" ht="136.5" thickBot="1">
+      <c r="A4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J2" s="11"/>
-    </row>
-    <row r="3" spans="1:10" ht="136.5" thickBot="1">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4" spans="1:10" ht="136.5" thickBot="1">
-      <c r="A4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J4" s="11"/>
-    </row>
-    <row r="5" spans="1:10" ht="136.5" thickBot="1">
-      <c r="A5" s="22" t="s">
+      <c r="J4" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" spans="1:11" ht="136.5" thickBot="1">
+      <c r="A5" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="H5" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="I5" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J5" s="11"/>
-    </row>
-    <row r="6" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="4" t="s">
+      <c r="J5" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A6" s="38"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="H6" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="11"/>
-    </row>
-    <row r="7" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="4" t="s">
+      <c r="I6" s="35"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A7" s="39"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="H7" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J7" s="11"/>
-    </row>
-    <row r="8" spans="1:10" ht="238.5" thickBot="1">
-      <c r="A8" s="3" t="s">
+      <c r="I7" s="36"/>
+      <c r="J7" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="1:11" ht="238.5" thickBot="1">
+      <c r="A8" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="E8" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="H8" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J8" s="11"/>
-    </row>
-    <row r="9" spans="1:10" ht="136.5" thickBot="1">
-      <c r="A9" s="22" t="s">
+      <c r="J8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="1:11" ht="136.5" thickBot="1">
+      <c r="A9" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="E9" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="I9" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J9" s="11"/>
-    </row>
-    <row r="10" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="4" t="s">
+      <c r="J9" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:11" ht="85.5" thickBot="1">
+      <c r="A10" s="38"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H10" s="20"/>
-      <c r="I10" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J10" s="11"/>
-    </row>
-    <row r="11" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="4" t="s">
+      <c r="I10" s="35"/>
+      <c r="J10" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A11" s="38"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H11" s="20"/>
-      <c r="I11" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="4" t="s">
+      <c r="I11" s="35"/>
+      <c r="J11" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K11" s="10"/>
+    </row>
+    <row r="12" spans="1:11" ht="85.5" thickBot="1">
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="20"/>
-      <c r="I12" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" spans="1:10" ht="34.5" thickBot="1">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="4" t="s">
+      <c r="I12" s="35"/>
+      <c r="J12" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J13" s="11"/>
-    </row>
-    <row r="14" spans="1:10" ht="119.5" thickBot="1">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="4" t="s">
+      <c r="I13" s="35"/>
+      <c r="J13" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" spans="1:11" ht="119.5" thickBot="1">
+      <c r="A14" s="38"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="H14" s="20"/>
-      <c r="I14" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J14" s="11"/>
-    </row>
-    <row r="15" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="4" t="s">
+      <c r="I14" s="35"/>
+      <c r="J14" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J15" s="11"/>
-    </row>
-    <row r="16" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A16" s="22" t="s">
+      <c r="I15" s="36"/>
+      <c r="J15" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A16" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="E16" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="I16" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" spans="1:10" ht="136.5" thickBot="1">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="4" t="s">
+      <c r="J16" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" spans="1:11" ht="136.5" thickBot="1">
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" spans="1:10" ht="153.5" thickBot="1">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="4" t="s">
+      <c r="I17" s="35"/>
+      <c r="J17" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" spans="1:11" ht="153.5" thickBot="1">
+      <c r="A18" s="38"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="H18" s="20"/>
-      <c r="I18" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="4" t="s">
+      <c r="I18" s="35"/>
+      <c r="J18" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K18" s="10"/>
+    </row>
+    <row r="19" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H19" s="21"/>
-      <c r="I19" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J19" s="11"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K19" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="H5:H7"/>
+  <mergeCells count="28">
+    <mergeCell ref="I16:I19"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="B9:B15"/>
+    <mergeCell ref="C9:C15"/>
+    <mergeCell ref="D9:D15"/>
+    <mergeCell ref="E9:E15"/>
+    <mergeCell ref="I9:I15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="F9:F15"/>
+    <mergeCell ref="F16:F19"/>
+    <mergeCell ref="I5:I7"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="E5:E7"/>
-    <mergeCell ref="H16:H19"/>
-    <mergeCell ref="A9:A15"/>
-    <mergeCell ref="B9:B15"/>
-    <mergeCell ref="C9:C15"/>
-    <mergeCell ref="D9:D15"/>
-    <mergeCell ref="E9:E15"/>
-    <mergeCell ref="H9:H15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="D16:D19"/>
-    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F5:F7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:E19 G1:K19">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F19">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B9E59B-075D-41F5-B5CE-6398D79B6392}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="52.9140625" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.9140625" customWidth="1"/>
     <col min="2" max="2" width="27.58203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="52.58203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="52.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="52.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.9140625" customWidth="1"/>
+    <col min="6" max="6" width="15.9140625" customWidth="1"/>
+    <col min="7" max="8" width="52.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A1" s="45" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="42" t="s">
-        <v>429</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>427</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>428</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>425</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:11" ht="85.5" thickBot="1">
+      <c r="A2" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="F2" s="37" t="str">
+        <f>_xlfn.CONCAT("TC-", A2)</f>
+        <v>TC-HTR-001</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K2" s="40"/>
+    </row>
+    <row r="3" spans="1:11" ht="136.5" thickBot="1">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="36"/>
+      <c r="J3" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K3" s="41"/>
+    </row>
+    <row r="4" spans="1:11" ht="136.5" thickBot="1">
+      <c r="A4" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J2" s="25"/>
-    </row>
-    <row r="3" spans="1:10" ht="136.5" thickBot="1">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J3" s="26"/>
-    </row>
-    <row r="4" spans="1:10" ht="136.5" thickBot="1">
-      <c r="A4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J4" s="11"/>
-    </row>
-    <row r="5" spans="1:10" ht="170.5" thickBot="1">
-      <c r="A5" s="22" t="s">
+      <c r="J4" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" spans="1:11" ht="170.5" thickBot="1">
+      <c r="A5" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="I5" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J5" s="11"/>
-    </row>
-    <row r="6" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="4" t="s">
+      <c r="J5" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A6" s="39"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J6" s="11"/>
-    </row>
-    <row r="7" spans="1:10" ht="153.5" thickBot="1">
-      <c r="A7" s="22" t="s">
+      <c r="I6" s="36"/>
+      <c r="J6" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="1:11" ht="153.5" thickBot="1">
+      <c r="A7" s="37" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="I7" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J7" s="11"/>
-    </row>
-    <row r="8" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A8" s="24"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="4" t="s">
+      <c r="J7" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A8" s="39"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H8" s="21"/>
-      <c r="I8" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J8" s="11"/>
-    </row>
-    <row r="9" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A9" s="3" t="s">
+      <c r="I8" s="36"/>
+      <c r="J8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A9" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="H9" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J9" s="11"/>
-    </row>
-    <row r="10" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A10" s="3" t="s">
+      <c r="J9" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A10" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="H10" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J10" s="11"/>
-    </row>
-    <row r="11" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A11" s="3" t="s">
+      <c r="J10" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A11" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A12" s="3" t="s">
+      <c r="J11" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K11" s="10"/>
+    </row>
+    <row r="12" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A12" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="H12" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A13" s="22" t="s">
+      <c r="J12" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A13" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="H13" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J13" s="11"/>
-    </row>
-    <row r="14" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="10" t="s">
+      <c r="I13" s="7"/>
+      <c r="J13" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A14" s="38"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="I14" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J14" s="11"/>
-    </row>
-    <row r="15" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="10" t="s">
+      <c r="J14" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="H15" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J15" s="11"/>
-    </row>
-    <row r="16" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A16" s="22" t="s">
+      <c r="I15" s="36"/>
+      <c r="J15" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="1:11" ht="85.5" thickBot="1">
+      <c r="A16" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="34" t="s">
         <v>206</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="I16" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="10" t="s">
+      <c r="J16" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="4" t="s">
+      <c r="I17" s="35"/>
+      <c r="J17" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" spans="1:11" ht="85.5" thickBot="1">
+      <c r="A18" s="38"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H18" s="20"/>
-      <c r="I18" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="4" t="s">
+      <c r="I18" s="35"/>
+      <c r="J18" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K18" s="10"/>
+    </row>
+    <row r="19" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H19" s="21"/>
-      <c r="I19" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J19" s="11"/>
-    </row>
-    <row r="20" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A20" s="22" t="s">
+      <c r="I19" s="36"/>
+      <c r="J19" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K19" s="10"/>
+    </row>
+    <row r="20" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A20" s="37" t="s">
         <v>211</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="H20" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="I20" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="I20" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J20" s="11"/>
-    </row>
-    <row r="21" spans="1:10" ht="119.5" thickBot="1">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="4" t="s">
+      <c r="J20" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K20" s="10"/>
+    </row>
+    <row r="21" spans="1:11" ht="119.5" thickBot="1">
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J21" s="11"/>
-    </row>
-    <row r="22" spans="1:10" ht="153.5" thickBot="1">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="10" t="s">
+      <c r="I21" s="35"/>
+      <c r="J21" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K21" s="10"/>
+    </row>
+    <row r="22" spans="1:11" ht="153.5" thickBot="1">
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="H22" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H22" s="20"/>
-      <c r="I22" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J22" s="25"/>
-    </row>
-    <row r="23" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="4" t="s">
+      <c r="I22" s="35"/>
+      <c r="J22" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K22" s="40"/>
+    </row>
+    <row r="23" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A23" s="39"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H23" s="21"/>
-      <c r="I23" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J23" s="26"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K23" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="J2:J3"/>
+  <mergeCells count="44">
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="F16:F19"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="E20:E23"/>
+    <mergeCell ref="I20:I23"/>
+    <mergeCell ref="F20:F23"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="I16:I19"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="K2:K3"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="H16:H19"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="D16:D19"/>
-    <mergeCell ref="E16:E19"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="E20:E23"/>
-    <mergeCell ref="H20:H23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:E23 G1:K23">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F23">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{155B3A87-78D4-48A9-8661-9106DEE143B0}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="52.9140625" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.9140625" customWidth="1"/>
     <col min="2" max="2" width="28.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="52.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="43.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.9140625" customWidth="1"/>
+    <col min="9" max="9" width="52.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="43.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A1" s="45" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="42" t="s">
-        <v>429</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>427</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>428</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>425</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:11" ht="85.5" thickBot="1">
+      <c r="A2" s="37" t="s">
         <v>212</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="37" t="str">
+        <f>_xlfn.CONCAT("TC-", A2)</f>
+        <v>TC-HDR-001</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I2" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="12" t="s">
+    <row r="3" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A4" s="22" t="s">
+      <c r="I3" s="36"/>
+      <c r="J3" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A4" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="I4" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J4" s="11"/>
-    </row>
-    <row r="5" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="4" t="s">
+      <c r="J4" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J5" s="11"/>
-    </row>
-    <row r="6" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="4" t="s">
+      <c r="I5" s="35"/>
+      <c r="J5" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A6" s="39"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="H6" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J6" s="11"/>
-    </row>
-    <row r="7" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A7" s="3" t="s">
+      <c r="I6" s="36"/>
+      <c r="J6" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A7" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J7" s="11"/>
-    </row>
-    <row r="8" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A8" s="3" t="s">
+      <c r="J7" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A8" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J8" s="11"/>
-    </row>
-    <row r="9" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A9" s="3" t="s">
+      <c r="J8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A9" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J9" s="11"/>
-    </row>
-    <row r="10" spans="1:10" ht="272.5" thickBot="1">
-      <c r="A10" s="22" t="s">
+      <c r="J9" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:11" ht="272.5" thickBot="1">
+      <c r="A10" s="37" t="s">
         <v>248</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="34" t="s">
         <v>250</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="37" t="s">
+        <v>248</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J10" s="11"/>
-    </row>
-    <row r="11" spans="1:10" ht="204.5" thickBot="1">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="4" t="s">
+      <c r="J10" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="1:11" ht="204.5" thickBot="1">
+      <c r="A11" s="38"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="I11" s="34" t="s">
         <v>258</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" spans="1:10" ht="119.5" thickBot="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="4" t="s">
+      <c r="J11" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K11" s="10"/>
+    </row>
+    <row r="12" spans="1:11" ht="119.5" thickBot="1">
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="H12" s="20"/>
-      <c r="I12" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="4" t="s">
+      <c r="I12" s="35"/>
+      <c r="J12" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="H13" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J13" s="11"/>
-    </row>
-    <row r="14" spans="1:10" ht="136.5" thickBot="1">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="4" t="s">
+      <c r="I13" s="35"/>
+      <c r="J13" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" spans="1:11" ht="136.5" thickBot="1">
+      <c r="A14" s="38"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="H14" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="H14" s="20"/>
-      <c r="I14" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J14" s="11"/>
-    </row>
-    <row r="15" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="4" t="s">
+      <c r="I14" s="35"/>
+      <c r="J14" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="H15" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J15" s="11"/>
-    </row>
-    <row r="16" spans="1:10" ht="170.5" thickBot="1">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="4" t="s">
+      <c r="I15" s="35"/>
+      <c r="J15" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="1:11" ht="170.5" thickBot="1">
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="4" t="s">
+      <c r="I16" s="35"/>
+      <c r="J16" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A18" s="3" t="s">
+      <c r="I17" s="36"/>
+      <c r="J17" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A18" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="H18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A19" s="3" t="s">
+      <c r="J18" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K18" s="10"/>
+    </row>
+    <row r="19" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A19" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="I19" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="I19" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A20" s="22" t="s">
+      <c r="J19" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A20" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="37" t="s">
         <v>283</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="34" t="s">
         <v>284</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="H20" s="27"/>
-      <c r="I20" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="4" t="s">
+      <c r="I20" s="42"/>
+      <c r="J20" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="H21" s="28"/>
-      <c r="I21" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="4" t="s">
+      <c r="I21" s="43"/>
+      <c r="J21" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K21" s="7"/>
+    </row>
+    <row r="22" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="H22" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="H22" s="28"/>
-      <c r="I22" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="4" t="s">
+      <c r="I22" s="43"/>
+      <c r="J22" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K22" s="7"/>
+    </row>
+    <row r="23" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A23" s="38"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="H23" s="28"/>
-      <c r="I23" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="4" t="s">
+      <c r="I23" s="43"/>
+      <c r="J23" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K23" s="7"/>
+    </row>
+    <row r="24" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="H24" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="H24" s="28"/>
-      <c r="I24" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="4" t="s">
+      <c r="I24" s="43"/>
+      <c r="J24" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K24" s="7"/>
+    </row>
+    <row r="25" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A25" s="38"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="H25" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="H25" s="28"/>
-      <c r="I25" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J25" s="8"/>
-    </row>
-    <row r="26" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="4" t="s">
+      <c r="I25" s="43"/>
+      <c r="J25" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K25" s="7"/>
+    </row>
+    <row r="26" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A26" s="39"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="H26" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="H26" s="29"/>
-      <c r="I26" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J26" s="8"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K26" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="H4:H6"/>
+  <mergeCells count="28">
+    <mergeCell ref="I20:I26"/>
+    <mergeCell ref="A10:A17"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="C10:C17"/>
+    <mergeCell ref="D10:D17"/>
+    <mergeCell ref="E10:E17"/>
+    <mergeCell ref="I11:I17"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="B20:B26"/>
+    <mergeCell ref="C20:C26"/>
+    <mergeCell ref="D20:D26"/>
+    <mergeCell ref="E20:E26"/>
+    <mergeCell ref="F10:F17"/>
+    <mergeCell ref="F20:F26"/>
+    <mergeCell ref="I4:I6"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="E4:E6"/>
-    <mergeCell ref="H20:H26"/>
-    <mergeCell ref="A10:A17"/>
-    <mergeCell ref="B10:B17"/>
-    <mergeCell ref="C10:C17"/>
-    <mergeCell ref="D10:D17"/>
-    <mergeCell ref="E10:E17"/>
-    <mergeCell ref="H11:H17"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="B20:B26"/>
-    <mergeCell ref="C20:C26"/>
-    <mergeCell ref="D20:D26"/>
-    <mergeCell ref="E20:E26"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:E26 G1:K26">
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F26">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F3A4CE-9737-4D17-B917-088AC2795166}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="52.9140625" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.9140625" customWidth="1"/>
     <col min="2" max="2" width="26.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.25" customWidth="1"/>
     <col min="4" max="4" width="47.4140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="52.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="51.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.9140625" customWidth="1"/>
+    <col min="7" max="7" width="89.4140625" customWidth="1"/>
+    <col min="8" max="8" width="52.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="87.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.5" thickBot="1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:11" ht="17.5" thickBot="1">
+      <c r="A1" s="45" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="42" t="s">
-        <v>429</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>427</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>428</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>425</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A2" s="37" t="s">
         <v>292</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="37" t="str">
+        <f>_xlfn.CONCAT("TC-", A2)</f>
+        <v>TC-HDC-001</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:10" ht="34.5" thickBot="1">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="4" t="s">
+      <c r="H2" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K2" s="7"/>
+    </row>
+    <row r="3" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="38"/>
+      <c r="G3" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="4" t="s">
+      <c r="I3" s="7"/>
+      <c r="J3" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="39"/>
+      <c r="G4" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A5" s="22" t="s">
+      <c r="I4" s="7"/>
+      <c r="J4" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K4" s="7"/>
+    </row>
+    <row r="5" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A5" s="37" t="s">
         <v>301</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="34" t="s">
         <v>302</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="4" t="s">
+      <c r="I5" s="7"/>
+      <c r="J5" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A6" s="38"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="38"/>
+      <c r="G6" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="4" t="s">
+      <c r="I6" s="7"/>
+      <c r="J6" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A7" s="39"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="39"/>
+      <c r="G7" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A8" s="22" t="s">
+      <c r="I7" s="7"/>
+      <c r="J7" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A8" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="34" t="s">
         <v>308</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="51.5" thickBot="1">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="4" t="s">
+      <c r="I8" s="7"/>
+      <c r="J8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A9" s="39"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="39"/>
+      <c r="G9" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A10" s="22" t="s">
+      <c r="I9" s="7"/>
+      <c r="J9" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A10" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="34" t="s">
         <v>313</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="I10" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" ht="153.5" thickBot="1">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="4" t="s">
+      <c r="J10" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:11" ht="119.5" thickBot="1">
+      <c r="A11" s="39"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="39"/>
+      <c r="G11" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A12" s="22" t="s">
+      <c r="I11" s="36"/>
+      <c r="J11" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A12" s="37" t="s">
         <v>318</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="37" t="s">
         <v>319</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="4" t="s">
+      <c r="I12" s="7"/>
+      <c r="J12" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="1:10" ht="34.5" thickBot="1">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="4" t="s">
+      <c r="I13" s="7"/>
+      <c r="J13" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A14" s="38"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:10" ht="170.5" thickBot="1">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="4" t="s">
+      <c r="I14" s="7"/>
+      <c r="J14" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="4" t="s">
+      <c r="I15" s="7"/>
+      <c r="J15" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" ht="85.5" thickBot="1">
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J16" s="7" t="s">
+      <c r="I16" s="7"/>
+      <c r="J16" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K16" s="6" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="4" t="s">
+    <row r="17" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J17" s="7" t="s">
+      <c r="I17" s="7"/>
+      <c r="J17" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K17" s="6" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A18" s="22" t="s">
+    <row r="18" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A18" s="37" t="s">
         <v>334</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="37" t="s">
         <v>335</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="34" t="s">
+        <v>444</v>
+      </c>
+      <c r="D18" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="E18" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A19" s="38"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="H20" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="1:11" ht="85.5" thickBot="1">
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="J22" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="102.5" thickBot="1">
+      <c r="A23" s="37" t="s">
+        <v>341</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>342</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="E23" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F23" s="37" t="s">
+        <v>341</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" ht="34.5" thickBot="1">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="4" t="s">
+      <c r="I23" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K23" s="7"/>
+    </row>
+    <row r="24" spans="1:11" ht="68.5" thickBot="1">
+      <c r="A24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="I24" s="35"/>
+      <c r="J24" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K24" s="7"/>
+    </row>
+    <row r="25" spans="1:11" ht="34.5" thickBot="1">
+      <c r="A25" s="38"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="I25" s="35"/>
+      <c r="J25" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K25" s="7"/>
+    </row>
+    <row r="26" spans="1:11" ht="85.5" thickBot="1">
+      <c r="A26" s="38"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="H26" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="I26" s="35"/>
+      <c r="J26" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="51.5" thickBot="1">
+      <c r="A27" s="39"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="H21" s="8"/>
-      <c r="I21" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="H22" s="8"/>
-      <c r="I22" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J22" s="7" t="s">
+      <c r="I27" s="36"/>
+      <c r="J27" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K27" s="6" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="102.5" thickBot="1">
-      <c r="A23" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>343</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>322</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10" ht="119.5" thickBot="1">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="H24" s="20"/>
-      <c r="I24" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="1:10" ht="34.5" thickBot="1">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="H25" s="20"/>
-      <c r="I25" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J25" s="8"/>
-    </row>
-    <row r="26" spans="1:10" ht="85.5" thickBot="1">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="H26" s="20"/>
-      <c r="I26" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="68.5" thickBot="1">
-      <c r="A27" s="24"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="H27" s="21"/>
-      <c r="I27" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>333</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="C12:C17"/>
-    <mergeCell ref="D12:D17"/>
-    <mergeCell ref="E12:E17"/>
-    <mergeCell ref="H23:H27"/>
+  <mergeCells count="40">
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F17"/>
+    <mergeCell ref="I23:I27"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="B18:B22"/>
     <mergeCell ref="C18:C22"/>
@@ -7088,8 +7751,47 @@
     <mergeCell ref="C23:C27"/>
     <mergeCell ref="D23:D27"/>
     <mergeCell ref="E23:E27"/>
+    <mergeCell ref="F18:F22"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="C12:C17"/>
+    <mergeCell ref="D12:D17"/>
+    <mergeCell ref="E12:E17"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:E27 G1:K27">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F27">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7106,90 +7808,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.5" thickBot="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="17.5" thickBot="1">
+      <c r="A2" s="15">
+        <v>46113</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="17.5" thickBot="1">
-      <c r="A2" s="16">
+      <c r="D2" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:7" ht="85.5" thickBot="1">
+      <c r="A3" s="15">
         <v>46113</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="B3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="G2" s="11"/>
-    </row>
-    <row r="3" spans="1:7" ht="85.5" thickBot="1">
-      <c r="A3" s="16">
+      <c r="F3" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="1:7" ht="68.5" thickBot="1">
+      <c r="A4" s="15">
         <v>46113</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="B4" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="G3" s="11"/>
-    </row>
-    <row r="4" spans="1:7" ht="68.5" thickBot="1">
-      <c r="A4" s="16">
-        <v>46113</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs/제품 TEST 관리.xlsx
+++ b/docs/제품 TEST 관리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\product_test_tracing_system\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AA1C9A-1049-465C-8754-CC89B9E11B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800E3D15-F017-441B-9770-128CB37DF5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{421B0B10-1399-475F-B14E-2C2D39CF6739}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{421B0B10-1399-475F-B14E-2C2D39CF6739}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Config ID 관리" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="459">
   <si>
     <t>HRK-9000A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2001,9 +2001,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>STR(Steps To Reproduce)</t>
-  </si>
-  <si>
     <t>STR Completion Criteria</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2152,6 +2149,52 @@
   <si>
     <t>Test Case ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Config Reproducing Procedure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TC-HDC-001</t>
+  </si>
+  <si>
+    <t>TC-HDC-002</t>
+  </si>
+  <si>
+    <t>- HDR-9000 1대
+테스트환경 구성 : 
+- AP(2.4GHz) 1대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TC-HDC-007</t>
+  </si>
+  <si>
+    <t>TC-HDC-003</t>
+  </si>
+  <si>
+    <t>TC-HDC-004</t>
+  </si>
+  <si>
+    <t>TC-HDC-005</t>
+  </si>
+  <si>
+    <t>TC-HDC-006</t>
+  </si>
+  <si>
+    <t>TC-HRK-001</t>
+  </si>
+  <si>
+    <t>TC-HDR-001</t>
+  </si>
+  <si>
+    <t>TC-HDR-002</t>
+  </si>
+  <si>
+    <t>TC-HTR-001</t>
+  </si>
+  <si>
+    <t>TC-HLM-001</t>
   </si>
 </sst>
 </file>
@@ -2428,7 +2471,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2582,12 +2625,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="강조색1" xfId="1" builtinId="29"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -3039,7 +3099,7 @@
     <col min="5" max="5" width="37.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.75" customWidth="1"/>
     <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="48.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="32.08203125" customWidth="1"/>
     <col min="10" max="10" width="53.83203125" customWidth="1"/>
     <col min="11" max="11" width="53.9140625" customWidth="1"/>
@@ -3049,7 +3109,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="27" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -3058,7 +3118,7 @@
       <c r="F1" s="27"/>
       <c r="G1" s="27"/>
       <c r="H1" s="27" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
@@ -3066,34 +3126,34 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="23" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>411</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>409</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="I2" s="23" t="s">
         <v>412</v>
       </c>
-      <c r="I2" s="23" t="s">
-        <v>413</v>
-      </c>
       <c r="J2" s="24" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>369</v>
@@ -3102,7 +3162,7 @@
         <v>8</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3113,7 +3173,7 @@
         <v>407</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D3" s="45" t="s">
         <v>0</v>
@@ -3126,7 +3186,7 @@
       </c>
       <c r="G3" s="45"/>
       <c r="H3" s="45" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
@@ -3142,7 +3202,7 @@
         <v>407</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D4" s="45" t="s">
         <v>3</v>
@@ -3155,7 +3215,7 @@
       </c>
       <c r="G4" s="45"/>
       <c r="H4" s="45" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
@@ -3171,10 +3231,10 @@
         <v>407</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E5" s="45" t="s">
         <v>8</v>
@@ -3198,7 +3258,7 @@
         <v>407</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D6" s="45" t="s">
         <v>4</v>
@@ -3225,7 +3285,7 @@
         <v>407</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D7" s="45" t="s">
         <v>5</v>
@@ -3252,7 +3312,7 @@
         <v>407</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>6</v>
@@ -3279,7 +3339,7 @@
         <v>407</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>361</v>
@@ -3307,7 +3367,7 @@
         <v>405</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E10" s="48" t="s">
         <v>406</v>
@@ -3317,7 +3377,7 @@
       </c>
       <c r="G10" s="45"/>
       <c r="H10" s="45" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
@@ -3336,7 +3396,7 @@
         <v>405</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>365</v>
@@ -3347,17 +3407,17 @@
         <v>370</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K11" s="15"/>
       <c r="L11" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="102" customHeight="1">
@@ -3371,7 +3431,7 @@
         <v>405</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>403</v>
@@ -3406,7 +3466,7 @@
         <v>405</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>364</v>
@@ -3443,7 +3503,7 @@
         <v>405</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>367</v>
@@ -3478,7 +3538,7 @@
         <v>405</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>366</v>
@@ -3511,7 +3571,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E16" s="45"/>
       <c r="F16" s="45"/>
@@ -3534,7 +3594,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E17" s="45"/>
       <c r="F17" s="45"/>
@@ -3557,7 +3617,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E18" s="45"/>
       <c r="F18" s="45"/>
@@ -3580,7 +3640,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="45" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E19" s="45"/>
       <c r="F19" s="45"/>
@@ -3603,7 +3663,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="45" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E20" s="45"/>
       <c r="F20" s="45"/>
@@ -3626,7 +3686,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="45" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E21" s="45"/>
       <c r="F21" s="45"/>
@@ -3649,7 +3709,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="45" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E22" s="45"/>
       <c r="F22" s="45"/>
@@ -3668,7 +3728,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:M22">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3883,13 +3943,13 @@
         <v>13</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>14</v>
@@ -4001,7 +4061,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" thickBot="1">
       <c r="A1" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>11</v>
@@ -4013,16 +4073,16 @@
         <v>13</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>14</v>
@@ -4050,9 +4110,8 @@
       <c r="E2" s="29" t="s">
         <v>397</v>
       </c>
-      <c r="F2" s="32" t="str">
-        <f>_xlfn.CONCAT("TC-", A2)</f>
-        <v>TC-HRK-001</v>
+      <c r="F2" s="32" t="s">
+        <v>454</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>20</v>
@@ -4366,7 +4425,7 @@
         <v>65</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
@@ -4416,7 +4475,7 @@
         <v>72</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
@@ -4466,7 +4525,7 @@
         <v>72</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I20" s="31"/>
       <c r="J20" s="31"/>
@@ -4516,7 +4575,7 @@
         <v>85</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I22" s="31"/>
       <c r="J22" s="31"/>
@@ -7182,27 +7241,27 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:E26 A43:E50 E35:E42 G35:K50 G1:K26">
-    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:E27 B28:E34 G27:K34">
-    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",A27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F26 F43:F50">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",F27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7230,7 +7289,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" thickBot="1">
       <c r="A1" s="40" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -7242,16 +7301,16 @@
         <v>13</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>14</v>
@@ -7279,9 +7338,8 @@
       <c r="E2" s="29" t="s">
         <v>395</v>
       </c>
-      <c r="F2" s="32" t="str">
-        <f>_xlfn.CONCAT("TC-", A2)</f>
-        <v>TC-HLM-001</v>
+      <c r="F2" s="32" t="s">
+        <v>458</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>128</v>
@@ -10133,17 +10191,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:E19 G1:K19">
-    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10170,7 +10228,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" thickBot="1">
       <c r="A1" s="40" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -10182,16 +10240,16 @@
         <v>13</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>14</v>
@@ -10219,9 +10277,8 @@
       <c r="E2" s="29" t="s">
         <v>393</v>
       </c>
-      <c r="F2" s="32" t="str">
-        <f>_xlfn.CONCAT("TC-", A2)</f>
-        <v>TC-HTR-001</v>
+      <c r="F2" s="32" t="s">
+        <v>457</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>166</v>
@@ -13189,17 +13246,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:E23 G1:K23">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F23">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13224,7 +13281,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" thickBot="1">
       <c r="A1" s="40" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -13236,16 +13293,16 @@
         <v>13</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>14</v>
@@ -13270,12 +13327,11 @@
       <c r="D2" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="E2" s="29" t="s">
-        <v>215</v>
-      </c>
-      <c r="F2" s="32" t="str">
-        <f>_xlfn.CONCAT("TC-", A2)</f>
-        <v>TC-HDR-001</v>
+      <c r="E2" s="51" t="s">
+        <v>448</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>455</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>216</v>
@@ -13329,7 +13385,7 @@
         <v>215</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>220</v>
+        <v>456</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>222</v>
@@ -13399,8 +13455,9 @@
       <c r="E7" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>226</v>
+      <c r="F7" s="2" t="str">
+        <f>_xlfn.CONCAT("TC-",A7)</f>
+        <v>TC-HDR-003</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>231</v>
@@ -13432,8 +13489,9 @@
       <c r="E8" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>234</v>
+      <c r="F8" s="2" t="str">
+        <f t="shared" ref="F8:F9" si="0">_xlfn.CONCAT("TC-",A8)</f>
+        <v>TC-HDR-004</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>239</v>
@@ -13465,8 +13523,9 @@
       <c r="E9" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>241</v>
+      <c r="F9" s="2" t="str">
+        <f>_xlfn.CONCAT("TC-",A9)</f>
+        <v>TC-HDR-005</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>245</v>
@@ -13498,8 +13557,9 @@
       <c r="E10" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="F10" s="32" t="s">
-        <v>248</v>
+      <c r="F10" s="32" t="str">
+        <f t="shared" ref="F10:F17" si="1">_xlfn.CONCAT("TC-",A10)</f>
+        <v>TC-HDR-006</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>253</v>
@@ -13521,7 +13581,10 @@
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
-      <c r="F11" s="33"/>
+      <c r="F11" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>TC-</v>
+      </c>
       <c r="G11" s="3" t="s">
         <v>256</v>
       </c>
@@ -13542,7 +13605,10 @@
       <c r="C12" s="30"/>
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
-      <c r="F12" s="33"/>
+      <c r="F12" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>TC-</v>
+      </c>
       <c r="G12" s="3" t="s">
         <v>259</v>
       </c>
@@ -13561,7 +13627,10 @@
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30"/>
-      <c r="F13" s="33"/>
+      <c r="F13" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>TC-</v>
+      </c>
       <c r="G13" s="3" t="s">
         <v>48</v>
       </c>
@@ -13580,7 +13649,10 @@
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>
-      <c r="F14" s="33"/>
+      <c r="F14" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>TC-</v>
+      </c>
       <c r="G14" s="3" t="s">
         <v>262</v>
       </c>
@@ -13599,7 +13671,10 @@
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
-      <c r="F15" s="33"/>
+      <c r="F15" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>TC-</v>
+      </c>
       <c r="G15" s="3" t="s">
         <v>48</v>
       </c>
@@ -13618,7 +13693,10 @@
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
       <c r="E16" s="30"/>
-      <c r="F16" s="33"/>
+      <c r="F16" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>TC-</v>
+      </c>
       <c r="G16" s="3" t="s">
         <v>265</v>
       </c>
@@ -13637,7 +13715,10 @@
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
-      <c r="F17" s="34"/>
+      <c r="F17" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v>TC-</v>
+      </c>
       <c r="G17" s="3" t="s">
         <v>177</v>
       </c>
@@ -13666,8 +13747,9 @@
       <c r="E18" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>268</v>
+      <c r="F18" s="2" t="str">
+        <f>_xlfn.CONCAT("TC-",A18)</f>
+        <v>TC-HDR-007</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>7</v>
@@ -13699,8 +13781,9 @@
       <c r="E19" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>274</v>
+      <c r="F19" s="2" t="str">
+        <f>_xlfn.CONCAT("TC-",A19)</f>
+        <v>TC-HDR-008</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>279</v>
@@ -13732,8 +13815,9 @@
       <c r="E20" s="29" t="s">
         <v>278</v>
       </c>
-      <c r="F20" s="32" t="s">
-        <v>282</v>
+      <c r="F20" s="32" t="str">
+        <f t="shared" ref="F20:F26" si="2">_xlfn.CONCAT("TC-",A20)</f>
+        <v>TC-HDR-009</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>279</v>
@@ -13753,7 +13837,10 @@
       <c r="C21" s="30"/>
       <c r="D21" s="30"/>
       <c r="E21" s="30"/>
-      <c r="F21" s="33"/>
+      <c r="F21" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v>TC-</v>
+      </c>
       <c r="G21" s="3" t="s">
         <v>286</v>
       </c>
@@ -13772,7 +13859,10 @@
       <c r="C22" s="30"/>
       <c r="D22" s="30"/>
       <c r="E22" s="30"/>
-      <c r="F22" s="33"/>
+      <c r="F22" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v>TC-</v>
+      </c>
       <c r="G22" s="3" t="s">
         <v>288</v>
       </c>
@@ -13791,7 +13881,10 @@
       <c r="C23" s="30"/>
       <c r="D23" s="30"/>
       <c r="E23" s="30"/>
-      <c r="F23" s="33"/>
+      <c r="F23" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v>TC-</v>
+      </c>
       <c r="G23" s="3" t="s">
         <v>279</v>
       </c>
@@ -13810,7 +13903,10 @@
       <c r="C24" s="30"/>
       <c r="D24" s="30"/>
       <c r="E24" s="30"/>
-      <c r="F24" s="33"/>
+      <c r="F24" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v>TC-</v>
+      </c>
       <c r="G24" s="3" t="s">
         <v>151</v>
       </c>
@@ -13829,7 +13925,10 @@
       <c r="C25" s="30"/>
       <c r="D25" s="30"/>
       <c r="E25" s="30"/>
-      <c r="F25" s="33"/>
+      <c r="F25" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v>TC-</v>
+      </c>
       <c r="G25" s="3" t="s">
         <v>154</v>
       </c>
@@ -13848,7 +13947,10 @@
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
       <c r="E26" s="31"/>
-      <c r="F26" s="34"/>
+      <c r="F26" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v>TC-</v>
+      </c>
       <c r="G26" s="3" t="s">
         <v>279</v>
       </c>
@@ -16222,17 +16324,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:E26 G1:K26">
-    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F26">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16260,7 +16362,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" thickBot="1">
       <c r="A1" s="40" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -16272,16 +16374,16 @@
         <v>13</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>14</v>
@@ -16309,9 +16411,8 @@
       <c r="E2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F2" s="32" t="str">
-        <f>_xlfn.CONCAT("TC-", A2)</f>
-        <v>TC-HDC-001</v>
+      <c r="F2" s="32" t="s">
+        <v>446</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>296</v>
@@ -16384,7 +16485,7 @@
         <v>295</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>301</v>
+        <v>447</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>303</v>
@@ -16457,7 +16558,7 @@
         <v>295</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>305</v>
+        <v>450</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>303</v>
@@ -16509,7 +16610,7 @@
         <v>295</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>311</v>
+        <v>451</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>303</v>
@@ -16563,7 +16664,7 @@
         <v>322</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>318</v>
+        <v>452</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>303</v>
@@ -16684,7 +16785,7 @@
         <v>335</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D18" s="29" t="s">
         <v>336</v>
@@ -16693,7 +16794,7 @@
         <v>322</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>334</v>
+        <v>453</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>303</v>
@@ -16804,7 +16905,7 @@
         <v>322</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>341</v>
+        <v>449</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>303</v>
@@ -19261,18 +19362,23 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:E27 G1:K27">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F27">
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="TBD">
+  <conditionalFormatting sqref="F2 F8:F27">
+    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="TBD">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="TBD">
       <formula>NOT(ISERROR(SEARCH("TBD",F1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="TBD">
+      <formula>NOT(ISERROR(SEARCH("TBD",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
